--- a/Jaipur-March-2026.xlsx
+++ b/Jaipur-March-2026.xlsx
@@ -112,13 +112,13 @@
     <t>MH02FG4104</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>ETIOS</t>
   </si>
   <si>
-    <t>Dzire</t>
+    <t>DZIRE</t>
   </si>
   <si>
     <t>16/08/2018</t>
